--- a/ig/DM-JUIN-2026/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-TRE-A06-FormatCodeComplementaire.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="191">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251029120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-29T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,7 +118,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>63</t>
+    <t>68</t>
   </si>
   <si>
     <t>Code</t>
@@ -557,6 +557,36 @@
   </si>
   <si>
     <t>Test rapide d'orientation diagnostique</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:mso-rougeole:2026</t>
+  </si>
+  <si>
+    <t>Déclaration de maladie à signalement obligatoire : Rougeole</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:mso-dengue:2026</t>
+  </si>
+  <si>
+    <t>Déclaration de maladie à signalement obligatoire : Dengue</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:mso-chikungunya:2026</t>
+  </si>
+  <si>
+    <t>Déclaration de maladie à signalement obligatoire : Chikungunya</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:mso-zika:2026</t>
+  </si>
+  <si>
+    <t>Déclaration de maladie à signalement obligatoire : Zika</t>
+  </si>
+  <si>
+    <t>urn:ans:ci-sis:mso-westnile:2026</t>
+  </si>
+  <si>
+    <t>Déclaration de maladie à signalement obligatoire : West Nile</t>
   </si>
 </sst>
 </file>
@@ -972,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D64"/>
+  <dimension ref="A1:D69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1749,6 +1779,66 @@
       </c>
       <c r="D64" s="2"/>
     </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="D65" s="2"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="D66" s="2"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="D67" s="2"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="D68" s="2"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="D69" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
